--- a/ig/nr-INS-Patient/StructureDefinition-fr-core-practitioner.xlsx
+++ b/ig/nr-INS-Patient/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-16T12:02:48+00:00</t>
+    <t>2023-10-16T13:03:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -331,7 +331,7 @@
     <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:meta.profile}
+    <t xml:space="preserve">value:$this}
 </t>
   </si>
   <si>
@@ -2237,7 +2237,7 @@
     <col min="25" max="25" width="98.61328125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="97.73828125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="1.04296875" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="19.0078125" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="14.46484375" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="1.04296875" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="5.62109375" customWidth="true" bestFit="true" hidden="true"/>
